--- a/backtest_runs/20260410_193731/by_symbol/FHAM/FHAM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FHAM/FHAM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>107196.05</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>109940.59</v>
@@ -817,7 +817,7 @@
         <v>-836.75</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>109103.84</v>
@@ -1185,7 +1185,7 @@
         <v>-3146.180000000004</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>109438.54</v>
@@ -1231,7 +1231,7 @@
         <v>-870.2200000000053</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>108568.32</v>
@@ -1277,7 +1277,7 @@
         <v>-468.57999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>108099.74</v>
@@ -1369,7 +1369,7 @@
         <v>-8200.150000000009</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>99899.59</v>
@@ -1645,7 +1645,7 @@
         <v>-1706.969999999993</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>108668.73</v>
